--- a/results/Int Task Remove ACC -0.1/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_6_permute.xlsx
@@ -440,647 +440,647 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6962360771076608</v>
+        <v>0.6794731895621897</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.690943778592559</v>
+        <v>0.6741209688828256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6934384329047472</v>
+        <v>0.6617817337419454</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6591726416122936</v>
+        <v>0.6617817337419454</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6675175914353656</v>
+        <v>0.6617817337419454</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6603300855219941</v>
+        <v>0.6565036273183795</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6427922647244075</v>
+        <v>0.6565036273183795</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6346489327096623</v>
+        <v>0.6372438327477782</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6361147730211494</v>
+        <v>0.6325836454842566</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6428533132451411</v>
+        <v>0.608577610015742</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6441916500040999</v>
+        <v>0.6126056860276832</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6506675238990316</v>
+        <v>0.5998305509324879</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6506675238990316</v>
+        <v>0.5961861119346028</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6503514682732414</v>
+        <v>0.5799931607635075</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6482339181075769</v>
+        <v>0.5860984633794479</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6319941105072839</v>
+        <v>0.5860712055528472</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6218607318794024</v>
+        <v>0.584879970949014</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6122918831148352</v>
+        <v>0.5888339327051568</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.614134827572846</v>
+        <v>0.586937598950416</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6258692092887465</v>
+        <v>0.593749127073735</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6258692092887465</v>
+        <v>0.5886050570702297</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6084588920436882</v>
+        <v>0.5994381283379574</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6067849010563422</v>
+        <v>0.615602695325981</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6266222912253226</v>
+        <v>0.6047653439036632</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6358424200264379</v>
+        <v>0.6009596106591168</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6214390240166232</v>
+        <v>0.6036973326977679</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6270604438925799</v>
+        <v>0.5899609649901376</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5729169388694806</v>
+        <v>0.5595009069422305</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5599390596094878</v>
+        <v>0.5594943740746982</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5682436858708944</v>
+        <v>0.5612762700119754</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5724472482210325</v>
+        <v>0.5526981643993862</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5644990011470814</v>
+        <v>0.555710492145691</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5621525753464898</v>
+        <v>0.5673718859622644</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5642843176036901</v>
+        <v>0.550393188516931</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5567665639729926</v>
+        <v>0.5498417243886813</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5567665639729926</v>
+        <v>0.543407300411886</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.558602975563471</v>
+        <v>0.5473950528621619</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5507691663069835</v>
+        <v>0.5363734295211724</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5425855107305728</v>
+        <v>0.5327627812174202</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5400570657242517</v>
+        <v>0.52578995884744</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.523475071028039</v>
+        <v>0.5289570479728737</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5219972913379584</v>
+        <v>0.5343365264788384</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5232615138411189</v>
+        <v>0.5343365264788384</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5232615138411189</v>
+        <v>0.5229116675211958</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5092199035298209</v>
+        <v>0.5172161333894409</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4658319764492378</v>
+        <v>0.5231601417587201</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4583468871562022</v>
+        <v>0.5226010184064669</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4612317113499788</v>
+        <v>0.5122790877053235</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4612317113499788</v>
+        <v>0.5024878961733615</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4612317113499788</v>
+        <v>0.502844275360817</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4686458401853352</v>
+        <v>0.5005577717244878</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4715034065525112</v>
+        <v>0.5019157070860437</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4648597055433858</v>
+        <v>0.5019157070860437</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4506306695152973</v>
+        <v>0.4841381976314075</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4523722418909092</v>
+        <v>0.4907273829873317</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4562674078392608</v>
+        <v>0.4987060416860024</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4525630466771133</v>
+        <v>0.4987060416860024</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4257800919647531</v>
+        <v>0.4838383615388012</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4320128981332219</v>
+        <v>0.4890317659557405</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4330755028280558</v>
+        <v>0.4939208288541891</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4369488174608681</v>
+        <v>0.4982246369302551</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.402708031282073</v>
+        <v>0.5000806471233306</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.402708031282073</v>
+        <v>0.4996839443742099</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4164630965071235</v>
+        <v>0.5000806471233306</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4124960690159159</v>
+        <v>0.5001209706849959</v>
       </c>
     </row>
     <row r="67">
@@ -1090,197 +1090,197 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4286966794110147</v>
+        <v>0.5007934054982415</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4397793512727378</v>
+        <v>0.500437026310786</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4330550031402818</v>
+        <v>0.5004773498724514</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4450989076144401</v>
+        <v>0.5001209706849959</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4382121388788518</v>
+        <v>0.5008740526215721</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4382121388788518</v>
+        <v>0.4998855621825364</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4411895495745526</v>
+        <v>0.499529182995081</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4404430005055088</v>
+        <v>0.4986213396793759</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4419426315111288</v>
+        <v>0.5002419413699919</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4673099814106128</v>
+        <v>0.4993340980542867</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4655170471799188</v>
+        <v>0.4997308008034075</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4655170471799188</v>
+        <v>0.4977538199253361</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4923022546052211</v>
+        <v>0.4932146033468106</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4919458754177656</v>
+        <v>0.4945997965349671</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4892496032972509</v>
+        <v>0.4992131273692909</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4893978318088474</v>
+        <v>0.4985406925560453</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4791162246693694</v>
+        <v>0.4988567481818354</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4834810812661688</v>
+        <v>0.4977134963636707</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.498101413532317</v>
+        <v>0.4945529401057693</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4975837400982003</v>
+        <v>0.5003967027491207</v>
       </c>
     </row>
     <row r="87">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5007181648859722</v>
+        <v>0.5003563791874555</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5021578737273299</v>
+        <v>0.5000403235616653</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5017208474165438</v>
+        <v>0.5000403235616653</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5020630345124634</v>
+        <v>0.5000403235616653</v>
       </c>
     </row>
   </sheetData>
